--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486378_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486378_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1598</v>
+        <v>3.5818</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9409</v>
+        <v>4.178</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7811</v>
+        <v>-0.5962</v>
       </c>
       <c r="G2" t="n">
         <v>2.6364</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5435</v>
+        <v>0.9656</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9718</v>
+        <v>1.2089</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4283</v>
+        <v>-0.2434</v>
       </c>
       <c r="V2" t="n">
         <v>-1.3252</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2655</v>
+        <v>3.287</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8643</v>
+        <v>6.2248</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.5987</v>
+        <v>-2.9378</v>
       </c>
       <c r="G3" t="n">
         <v>2.5177</v>
@@ -688,13 +688,13 @@
         <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5839</v>
+        <v>0.6054</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4194</v>
+        <v>-0.0589</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0033</v>
+        <v>0.6642</v>
       </c>
       <c r="V3" t="n">
         <v>1.469</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8633</v>
+        <v>2.4087</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7102</v>
+        <v>2.0707</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1531</v>
+        <v>0.3381</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1195</v>
@@ -766,13 +766,13 @@
         <v>2.3926</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2963</v>
+        <v>0.8418</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0601</v>
+        <v>0.4206</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2362</v>
+        <v>0.4212</v>
       </c>
       <c r="V4" t="n">
         <v>1.469</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. GALAN POZO</t>
+          <t>L. WESTERMANN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4785</v>
+        <v>1.8622</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5809</v>
+        <v>3.2544</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8976</v>
+        <v>-1.3922</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.6648</v>
+        <v>3.0386</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6143999999999999</v>
+        <v>1.5875</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.0504</v>
+        <v>1.4511</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.6326</v>
+        <v>5.1704</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0799</v>
+        <v>2.7009</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.7125</v>
+        <v>2.4695</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0322</v>
+        <v>-2.1318</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6943</v>
+        <v>-1.1134</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3379</v>
+        <v>-1.0184</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2175</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.305</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7964</v>
+        <v>-0.1541</v>
       </c>
       <c r="T5" t="n">
         <v>0.1286</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6677999999999999</v>
+        <v>-0.2827</v>
       </c>
       <c r="V5" t="n">
-        <v>4.1294</v>
+        <v>-0.3698</v>
       </c>
       <c r="W5" t="n">
-        <v>3.3899</v>
+        <v>-0.7395</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7395</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. WESTERMANN</t>
+          <t>A. GALAN POZO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4478</v>
+        <v>1.8583</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1174</v>
+        <v>1.0531</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6696</v>
+        <v>0.8052</v>
       </c>
       <c r="G6" t="n">
-        <v>3.0386</v>
+        <v>-3.6648</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5875</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4511</v>
+        <v>-3.0504</v>
       </c>
       <c r="J6" t="n">
-        <v>5.1704</v>
+        <v>-1.6326</v>
       </c>
       <c r="K6" t="n">
-        <v>2.7009</v>
+        <v>1.0799</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4695</v>
+        <v>-2.7125</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.1318</v>
+        <v>-2.0322</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1134</v>
+        <v>-1.6943</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0184</v>
+        <v>-0.3379</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.305</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5685</v>
+        <v>1.1762</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.6009</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5601</v>
+        <v>0.5753</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3698</v>
+        <v>4.1294</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7395</v>
+        <v>3.3899</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3698</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2747</v>
+        <v>-0.0212</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3402</v>
+        <v>-0.2717</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0655</v>
+        <v>0.2505</v>
       </c>
       <c r="G7" t="n">
         <v>-1.4601</v>
@@ -1000,13 +1000,13 @@
         <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0103</v>
+        <v>0.2638</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3341</v>
+        <v>0.4026</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3237</v>
+        <v>-0.1388</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5649999999999999</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>R. ANDERSSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4723</v>
+        <v>-0.7057</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4543</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.9266</v>
+        <v>-1.3423</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-1.4747</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4957</v>
+        <v>1.2713</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0829</v>
+        <v>-2.746</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3741</v>
+        <v>0.8746</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6091</v>
+        <v>2.1352</v>
       </c>
       <c r="L8" t="n">
-        <v>0.765</v>
+        <v>-1.2606</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.9613</v>
+        <v>-2.3493</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1134</v>
+        <v>-0.8639</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.8479</v>
+        <v>-1.4854</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3632</v>
+        <v>-0.3323</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0601</v>
+        <v>-0.2379</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3031</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5958</v>
+        <v>-0.4212</v>
       </c>
       <c r="W8" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.921</v>
+        <v>-0.4212</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. ANDERSSON</t>
+          <t>Y. BARRUETA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.228</v>
+        <v>-0.875</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0526</v>
+        <v>3.4176</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2806</v>
+        <v>-4.2926</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4747</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2713</v>
+        <v>-0.3409</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.746</v>
+        <v>-0.5275</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8746</v>
+        <v>3.1098</v>
       </c>
       <c r="K9" t="n">
-        <v>2.1352</v>
+        <v>1.3869</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2606</v>
+        <v>1.7228</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3493</v>
+        <v>-3.9782</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8639</v>
+        <v>-1.7278</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4854</v>
+        <v>-2.2504</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8546</v>
+        <v>0.1742</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.822</v>
+        <v>-0.0396</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0327</v>
+        <v>0.2139</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.4212</v>
+        <v>-1.921</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.4212</v>
+        <v>-2.4859</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Y. BARRUETA</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0546</v>
+        <v>-0.9402</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3613</v>
+        <v>2.4796</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.4159</v>
+        <v>-3.4198</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8683999999999999</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3409</v>
+        <v>0.4957</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5275</v>
+        <v>-1.0829</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1098</v>
+        <v>2.3741</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3869</v>
+        <v>1.6091</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7228</v>
+        <v>0.765</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.9782</v>
+        <v>-2.9613</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7278</v>
+        <v>-1.1134</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.2504</v>
+        <v>-1.8479</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7401</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9576</v>
+        <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0053</v>
+        <v>0.8953</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0959</v>
+        <v>0.0853</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0906</v>
+        <v>0.8099</v>
       </c>
       <c r="V10" t="n">
+        <v>-0.5958</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.3252</v>
+      </c>
+      <c r="X10" t="n">
         <v>-1.921</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-2.4859</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2708</v>
+        <v>-2.1715</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.671</v>
+        <v>-0.6025</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5998</v>
+        <v>-1.569</v>
       </c>
       <c r="G11" t="n">
         <v>-0.8309</v>
@@ -1312,13 +1312,13 @@
         <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5601</v>
+        <v>0.6594</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5396</v>
+        <v>0.6081</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="V11" t="n">
         <v>-1.13</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.914499999999999</v>
+        <v>8.2844</v>
       </c>
       <c r="E12" t="n">
-        <v>21.0707</v>
+        <v>22.4406</v>
       </c>
       <c r="F12" t="n">
         <v>-14.1561</v>
@@ -1381,7 +1381,7 @@
         <v>-9.116400000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>3.2627</v>
+        <v>3.262700000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-11.9628</v>
@@ -1390,16 +1390,16 @@
         <v>15.2254</v>
       </c>
       <c r="S12" t="n">
-        <v>3.7253</v>
+        <v>5.0953</v>
       </c>
       <c r="T12" t="n">
-        <v>1.7486</v>
+        <v>3.1186</v>
       </c>
       <c r="U12" t="n">
         <v>1.9767</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7394000000000005</v>
+        <v>0.7394000000000007</v>
       </c>
       <c r="W12" t="n">
         <v>10.1905</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.9486</v>
+        <v>3.23</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2088</v>
+        <v>3.7676</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2602</v>
+        <v>-0.5376</v>
       </c>
       <c r="G13" t="n">
         <v>2.8723</v>
@@ -1468,13 +1468,13 @@
         <v>1.5225</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8531</v>
+        <v>-0.5717</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.1142</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1802</v>
+        <v>-0.4576</v>
       </c>
       <c r="V13" t="n">
         <v>1.582</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>J. CREMO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7499</v>
+        <v>1.5708</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5894</v>
+        <v>4.0768</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.8395</v>
+        <v>-2.506</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7469</v>
+        <v>-1.0284</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3285</v>
+        <v>0.3406</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4184</v>
+        <v>-1.369</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5243</v>
+        <v>0.7758</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3713</v>
+        <v>0.2769</v>
       </c>
       <c r="L14" t="n">
-        <v>0.153</v>
+        <v>0.4989</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2712</v>
+        <v>-1.8042</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6998</v>
+        <v>0.0636</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5714</v>
+        <v>-1.8679</v>
       </c>
       <c r="P14" t="n">
         <v>1.0875</v>
@@ -1546,22 +1546,22 @@
         <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3922</v>
+        <v>-0.1833</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8051</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4129</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>1.017</v>
+        <v>1.695</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2599</v>
+        <v>3.3899</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.243</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.956</v>
+        <v>1.5264</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5271</v>
+        <v>2.9741</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.571</v>
+        <v>-1.4477</v>
       </c>
       <c r="G15" t="n">
         <v>4.1809</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3719</v>
+        <v>-0.8015</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8904</v>
+        <v>-0.4434</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4814</v>
+        <v>-0.3581</v>
       </c>
       <c r="V15" t="n">
         <v>-0.113</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. CREMO</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8155</v>
+        <v>1.2026</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6297</v>
+        <v>2.9189</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.8142</v>
+        <v>-1.7162</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0284</v>
+        <v>-0.7469</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3406</v>
+        <v>-0.3285</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.369</v>
+        <v>-0.4184</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7758</v>
+        <v>0.5243</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2769</v>
+        <v>0.3713</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4989</v>
+        <v>0.153</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8042</v>
+        <v>-1.2712</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0636</v>
+        <v>-0.6998</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8679</v>
+        <v>-0.5714</v>
       </c>
       <c r="P16" t="n">
         <v>1.0875</v>
@@ -1702,28 +1702,28 @@
         <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9385</v>
+        <v>-0.155</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.536</v>
+        <v>0.1346</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4026</v>
+        <v>-0.2896</v>
       </c>
       <c r="V16" t="n">
-        <v>1.695</v>
+        <v>1.017</v>
       </c>
       <c r="W16" t="n">
-        <v>3.3899</v>
+        <v>2.2599</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.695</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. CUEVAS SIMARRO</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.342</v>
+        <v>-0.2087</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9398</v>
+        <v>0.305</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.2818</v>
+        <v>-0.5138</v>
       </c>
       <c r="G17" t="n">
-        <v>4.4696</v>
+        <v>0.969</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9252</v>
+        <v>0.9125</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5444</v>
+        <v>0.0566</v>
       </c>
       <c r="J17" t="n">
-        <v>5.9248</v>
+        <v>3.6163</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1931</v>
+        <v>1.6274</v>
       </c>
       <c r="L17" t="n">
-        <v>3.7317</v>
+        <v>1.989</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4552</v>
+        <v>-2.6473</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2679</v>
+        <v>-0.7149</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1873</v>
+        <v>-1.9324</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.9576</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q17" t="n">
         <v>-3.2626</v>
       </c>
       <c r="R17" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0839</v>
+        <v>0.2578</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2776</v>
+        <v>-0.2439</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1937</v>
+        <v>0.5017</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.9379</v>
+        <v>0.7395</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.9379</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>D. CUEVAS SIMARRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3706</v>
+        <v>-0.7389</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0815</v>
+        <v>2.6045</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4521</v>
+        <v>-3.3435</v>
       </c>
       <c r="G18" t="n">
-        <v>0.969</v>
+        <v>4.4696</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9125</v>
+        <v>1.9252</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0566</v>
+        <v>2.5444</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6163</v>
+        <v>5.9248</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6274</v>
+        <v>2.1931</v>
       </c>
       <c r="L18" t="n">
-        <v>1.989</v>
+        <v>3.7317</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.6473</v>
+        <v>-1.4552</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7149</v>
+        <v>-0.2679</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.9324</v>
+        <v>-1.1873</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.1751</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q18" t="n">
         <v>-3.2626</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0959</v>
+        <v>-0.313</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4675</v>
+        <v>-0.0577</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5633</v>
+        <v>-0.2554</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7395</v>
+        <v>-2.9379</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5443</v>
+        <v>-2.9379</v>
       </c>
     </row>
     <row r="19">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0557</v>
+        <v>-1.626</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7763</v>
+        <v>1.3293</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.832</v>
+        <v>-2.9553</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4515</v>
@@ -2014,13 +2014,13 @@
         <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0822</v>
+        <v>-0.6525</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0601</v>
+        <v>-0.3869</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1423</v>
+        <v>-0.2656</v>
       </c>
       <c r="V20" t="n">
         <v>0.3904</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0747</v>
+        <v>-3.0058</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0055</v>
+        <v>-0.8703</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0691</v>
+        <v>-2.1355</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.409</v>
+        <v>-2.0509</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7665</v>
+        <v>-0.4867</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.1754</v>
+        <v>-1.5642</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1409</v>
+        <v>-0.5026</v>
       </c>
       <c r="K21" t="n">
-        <v>2.3787</v>
+        <v>0.1277</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.5196</v>
+        <v>-0.6303</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2681</v>
+        <v>-1.5484</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6123</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6558</v>
+        <v>-0.9339</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7401</v>
+        <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2945</v>
+        <v>-0.2599</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4627</v>
+        <v>-0.3677</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1681</v>
+        <v>0.1078</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.6127</v>
+        <v>-1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.3729</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2716</v>
+        <v>-3.9109</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.982</v>
+        <v>-0.5643</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2896</v>
+        <v>-3.3465</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0509</v>
+        <v>-2.409</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4867</v>
+        <v>0.7665</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5642</v>
+        <v>-3.1754</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5026</v>
+        <v>-0.1409</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1277</v>
+        <v>2.3787</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6303</v>
+        <v>-2.5196</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5484</v>
+        <v>-2.2681</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-1.6123</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9339</v>
+        <v>-0.6558</v>
       </c>
       <c r="P22" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>0.435</v>
+        <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.5417</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4795</v>
+        <v>-0.0961</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0463</v>
+        <v>-0.4455</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.13</v>
+        <v>-1.6127</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.13</v>
+        <v>-2.3729</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4031</v>
+        <v>-4.0871</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6895</v>
+        <v>-2.466</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7136</v>
+        <v>-1.6211</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0449</v>
@@ -2248,13 +2248,13 @@
         <v>1.0875</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9009</v>
+        <v>-0.5849</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6165</v>
+        <v>-0.3929</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2844</v>
+        <v>-0.192</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3698</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.9147</v>
+        <v>-6.9146</v>
       </c>
       <c r="E24" t="n">
         <v>14.1561</v>
       </c>
       <c r="F24" t="n">
-        <v>-21.0706</v>
+        <v>-21.0707</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8127000000000009</v>
+        <v>0.8127000000000004</v>
       </c>
       <c r="H24" t="n">
         <v>3.8928</v>
@@ -2326,10 +2326,10 @@
         <v>11.9626</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.7253</v>
+        <v>-3.7252</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.9768</v>
+        <v>-1.9766</v>
       </c>
       <c r="U24" t="n">
         <v>-1.7486</v>
